--- a/artfynd/A 32058-2022 artfynd.xlsx
+++ b/artfynd/A 32058-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32058-2022 artfynd.xlsx
+++ b/artfynd/A 32058-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,44 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64785892</v>
+        <v>70608105</v>
       </c>
       <c r="B2" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -721,13 +712,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562374.1299395014</v>
+        <v>562409</v>
       </c>
       <c r="R2" t="n">
-        <v>6465165.471699076</v>
+        <v>6465154</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,22 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-12-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-12-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-04-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +756,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,12 +777,7 @@
         <v>66042516</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562374.8388635891</v>
+        <v>562375</v>
       </c>
       <c r="R3" t="n">
-        <v>6465153.926038058</v>
+        <v>6465154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +848,9 @@
           <t>2017-04-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-04-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100162576</v>
+        <v>64785776</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,48 +889,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åtvidaberg, Ög</t>
+          <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562365.2987106136</v>
+        <v>562363</v>
       </c>
       <c r="R4" t="n">
-        <v>6465124.882803991</v>
+        <v>6465100</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-11-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-11-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,76 +963,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111357197</v>
+        <v>64843289</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Risten, Ög</t>
+          <t>Björksveden-Risten, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562360.3306950611</v>
+        <v>562324</v>
       </c>
       <c r="R5" t="n">
-        <v>6465139.513083479</v>
+        <v>6465127</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,22 +1053,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,6 +1083,1483 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110267634</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>562372</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6465193</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96970524</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>562326</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6465155</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>64785892</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björksveden-Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>562374</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6465165</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-12-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-12-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>98644628</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58067</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>562354</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6465187</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Nötkråkor har egentligen observerats regelbunden i området under de senaste 6 åren och särskilt på vintern. Längre in i skogsområdet finns det en s.k. fröplantering av vitgran i åldersklassen 10 till 20 år som ursakats av nötkråkan när den inte hittad igen sina gömda frön vilket bevisar en närvaro av nötkråkor under åtminstone 20 år i området!</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122700365</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>562375</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6465184</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100162576</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>562366</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6465125</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110106837</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>562336</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6465130</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>i häckningsrevir</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>93065983</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>562369</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6465186</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-05-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-05-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110267630</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>562372</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6465193</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>110267644</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>562345</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6465188</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>111357197</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>562360</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6465140</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-08-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129732505</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Byrum, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>562358</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6465194</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>96256837</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>562409</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6465154</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>96970532</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106231</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>562326</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6465155</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32058-2022 artfynd.xlsx
+++ b/artfynd/A 32058-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70608105</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66042516</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64785776</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64843289</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110267634</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96970524</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64785892</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98644628</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1608,6 +1653,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700365</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100162576</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1822,6 +1877,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110106837</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93065983</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2034,6 +2099,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110267630</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110267644</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2246,6 +2321,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357197</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2352,6 +2432,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129732505</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2458,6 +2543,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96256837</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2560,8 +2650,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96970532</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>